--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">4%</t>
+    <t xml:space="preserve">3.8%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,25 +53,31 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">8%</t>
+    <t xml:space="preserve">11.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4%</t>
   </si>
   <si>
     <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16%</t>
   </si>
   <si>
     <t xml:space="preserve">CA6</t>
@@ -481,36 +487,36 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -530,13 +536,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -556,13 +562,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -574,21 +580,21 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -608,13 +614,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -634,7 +640,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -660,7 +666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -686,13 +692,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -704,21 +710,21 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -738,7 +744,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -764,7 +770,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8%</t>
+    <t xml:space="preserve">2.8%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,7 +53,19 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5%</t>
+    <t xml:space="preserve">13.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -62,25 +74,25 @@
     <t xml:space="preserve">66.7%</t>
   </si>
   <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7%</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
+    <t xml:space="preserve">19.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4%</t>
   </si>
   <si>
     <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6%</t>
   </si>
   <si>
     <t xml:space="preserve">CA7</t>
@@ -487,16 +499,16 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -513,36 +525,36 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -562,39 +574,39 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -614,13 +626,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -640,7 +652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -666,65 +678,65 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -744,7 +756,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -770,22 +782,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8%</t>
+    <t xml:space="preserve">2.7%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,19 +53,16 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40%</t>
+    <t xml:space="preserve">16.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
   </si>
   <si>
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3%</t>
+    <t xml:space="preserve">8.1%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -80,7 +77,7 @@
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4%</t>
+    <t xml:space="preserve">18.9%</t>
   </si>
   <si>
     <t xml:space="preserve">28.6%</t>
@@ -92,7 +89,7 @@
     <t xml:space="preserve">CA6</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6%</t>
+    <t xml:space="preserve">5.4%</t>
   </si>
   <si>
     <t xml:space="preserve">CA7</t>
@@ -499,62 +496,62 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -574,13 +571,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -592,21 +589,21 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -626,13 +623,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -652,7 +649,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -678,65 +675,65 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>18</v>
-      </c>
-      <c r="H10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
         <v>17</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -756,7 +753,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -782,13 +779,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7%</t>
+    <t xml:space="preserve">1.9%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,64 +53,82 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2%</t>
+    <t xml:space="preserve">17%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
   </si>
   <si>
     <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
   </si>
 </sst>
 </file>
@@ -496,36 +514,36 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
         <v>6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -537,99 +555,99 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -649,7 +667,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -675,39 +693,39 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -719,30 +737,30 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -753,54 +771,54 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9%</t>
+    <t xml:space="preserve">1.8%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">17%</t>
+    <t xml:space="preserve">15.8%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -65,13 +65,49 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7%</t>
+    <t xml:space="preserve">5.3%</t>
   </si>
   <si>
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3%</t>
+    <t xml:space="preserve">12.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5%</t>
   </si>
   <si>
     <t xml:space="preserve">16.7%</t>
@@ -80,33 +116,6 @@
     <t xml:space="preserve">83.3%</t>
   </si>
   <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA10</t>
   </si>
   <si>
@@ -114,15 +123,6 @@
   </si>
   <si>
     <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75%</t>
   </si>
   <si>
     <t xml:space="preserve">CAFED</t>
@@ -566,19 +566,19 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -592,19 +592,19 @@
         <v>22</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -711,15 +711,15 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -771,28 +771,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8%</t>
+    <t xml:space="preserve">3.3%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8%</t>
+    <t xml:space="preserve">14.8%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -65,13 +65,55 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3%</t>
+    <t xml:space="preserve">4.9%</t>
   </si>
   <si>
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3%</t>
+    <t xml:space="preserve">13.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5%</t>
   </si>
   <si>
     <t xml:space="preserve">14.3%</t>
@@ -80,42 +122,6 @@
     <t xml:space="preserve">85.7%</t>
   </si>
   <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3%</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA10</t>
   </si>
   <si>
@@ -125,10 +131,10 @@
     <t xml:space="preserve">CADC</t>
   </si>
   <si>
+    <t xml:space="preserve">9.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
   </si>
 </sst>
 </file>
@@ -488,16 +494,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -566,19 +572,19 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -618,36 +624,36 @@
         <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -667,13 +673,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -693,33 +699,33 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -745,7 +751,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -771,13 +777,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" t="n">
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -797,28 +803,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>38</v>
-      </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
